--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 бррсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/19,10,26 Останкино КИ и ЗПФ/дв 19,10,26 бррсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\19,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA612437-CA76-42AA-B425-5E28B949AF65}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC88AB71-9F30-434B-82F0-8ADEF3CF256D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5574,7 +5574,8 @@
     <col min="22" max="31" width="6" customWidth="1"/>
     <col min="32" max="32" width="42.28515625" customWidth="1"/>
     <col min="33" max="33" width="7" customWidth="1"/>
-    <col min="34" max="50" width="3" customWidth="1"/>
+    <col min="34" max="34" width="7.140625" customWidth="1"/>
+    <col min="35" max="50" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:50" x14ac:dyDescent="0.25">
@@ -5979,7 +5980,10 @@
         <f>SUM(AG6:AG497)</f>
         <v>7424.1999999999989</v>
       </c>
-      <c r="AH5" s="5"/>
+      <c r="AH5" s="3">
+        <f>SUM(AH6:AH497)</f>
+        <v>877.21220000000005</v>
+      </c>
       <c r="AI5" s="5"/>
       <c r="AJ5" s="5"/>
       <c r="AK5" s="5"/>
@@ -6093,7 +6097,10 @@
         <f>G6*R6</f>
         <v>0</v>
       </c>
-      <c r="AH6" s="5"/>
+      <c r="AH6" s="5">
+        <f>P6*G6</f>
+        <v>1.0920000000000001</v>
+      </c>
       <c r="AI6" s="5"/>
       <c r="AJ6" s="5"/>
       <c r="AK6" s="5"/>
@@ -6208,7 +6215,10 @@
         <f t="shared" ref="AG7:AG70" si="8">G7*R7</f>
         <v>120.4</v>
       </c>
-      <c r="AH7" s="5"/>
+      <c r="AH7" s="5">
+        <f t="shared" ref="AH7:AH70" si="9">P7*G7</f>
+        <v>14.080000000000002</v>
+      </c>
       <c r="AI7" s="5"/>
       <c r="AJ7" s="5"/>
       <c r="AK7" s="5"/>
@@ -6323,7 +6333,10 @@
         <f t="shared" si="8"/>
         <v>7</v>
       </c>
-      <c r="AH8" s="5"/>
+      <c r="AH8" s="5">
+        <f t="shared" si="9"/>
+        <v>1.5513999999999999</v>
+      </c>
       <c r="AI8" s="5"/>
       <c r="AJ8" s="5"/>
       <c r="AK8" s="5"/>
@@ -6441,7 +6454,10 @@
         <f t="shared" si="8"/>
         <v>25</v>
       </c>
-      <c r="AH9" s="5"/>
+      <c r="AH9" s="5">
+        <f t="shared" si="9"/>
+        <v>3.95</v>
+      </c>
       <c r="AI9" s="5"/>
       <c r="AJ9" s="5"/>
       <c r="AK9" s="5"/>
@@ -6558,7 +6574,10 @@
         <f t="shared" si="8"/>
         <v>120</v>
       </c>
-      <c r="AH10" s="5"/>
+      <c r="AH10" s="5">
+        <f t="shared" si="9"/>
+        <v>15.0524</v>
+      </c>
       <c r="AI10" s="5"/>
       <c r="AJ10" s="5"/>
       <c r="AK10" s="5"/>
@@ -6675,7 +6694,10 @@
         <f t="shared" si="8"/>
         <v>60</v>
       </c>
-      <c r="AH11" s="5"/>
+      <c r="AH11" s="5">
+        <f t="shared" si="9"/>
+        <v>2.5140000000000002</v>
+      </c>
       <c r="AI11" s="5"/>
       <c r="AJ11" s="5"/>
       <c r="AK11" s="5"/>
@@ -6789,7 +6811,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="5"/>
+      <c r="AH12" s="5">
+        <f t="shared" si="9"/>
+        <v>2.4272</v>
+      </c>
       <c r="AI12" s="5"/>
       <c r="AJ12" s="5"/>
       <c r="AK12" s="5"/>
@@ -6907,7 +6932,10 @@
         <f t="shared" si="8"/>
         <v>100</v>
       </c>
-      <c r="AH13" s="5"/>
+      <c r="AH13" s="5">
+        <f t="shared" si="9"/>
+        <v>12.1724</v>
+      </c>
       <c r="AI13" s="5"/>
       <c r="AJ13" s="5"/>
       <c r="AK13" s="5"/>
@@ -7021,7 +7049,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="5"/>
+      <c r="AH14" s="5">
+        <f t="shared" si="9"/>
+        <v>1.25</v>
+      </c>
       <c r="AI14" s="5"/>
       <c r="AJ14" s="5"/>
       <c r="AK14" s="5"/>
@@ -7135,7 +7166,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH15" s="5"/>
+      <c r="AH15" s="5">
+        <f t="shared" si="9"/>
+        <v>1.9007999999999998</v>
+      </c>
       <c r="AI15" s="5"/>
       <c r="AJ15" s="5"/>
       <c r="AK15" s="5"/>
@@ -7253,7 +7287,10 @@
         <f t="shared" si="8"/>
         <v>112.5</v>
       </c>
-      <c r="AH16" s="5"/>
+      <c r="AH16" s="5">
+        <f t="shared" si="9"/>
+        <v>9.0500000000000007</v>
+      </c>
       <c r="AI16" s="5"/>
       <c r="AJ16" s="5"/>
       <c r="AK16" s="5"/>
@@ -7367,7 +7404,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="5"/>
+      <c r="AH17" s="5">
+        <f t="shared" si="9"/>
+        <v>3.28</v>
+      </c>
       <c r="AI17" s="5"/>
       <c r="AJ17" s="5"/>
       <c r="AK17" s="5"/>
@@ -7482,7 +7522,10 @@
         <f t="shared" si="8"/>
         <v>221</v>
       </c>
-      <c r="AH18" s="5"/>
+      <c r="AH18" s="5">
+        <f t="shared" si="9"/>
+        <v>35.301400000000001</v>
+      </c>
       <c r="AI18" s="5"/>
       <c r="AJ18" s="5"/>
       <c r="AK18" s="5"/>
@@ -7597,7 +7640,10 @@
         <f t="shared" si="8"/>
         <v>22</v>
       </c>
-      <c r="AH19" s="5"/>
+      <c r="AH19" s="5">
+        <f t="shared" si="9"/>
+        <v>2.4626000000000001</v>
+      </c>
       <c r="AI19" s="5"/>
       <c r="AJ19" s="5"/>
       <c r="AK19" s="5"/>
@@ -7709,7 +7755,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="5"/>
+      <c r="AH20" s="5">
+        <f t="shared" si="9"/>
+        <v>4.24</v>
+      </c>
       <c r="AI20" s="5"/>
       <c r="AJ20" s="5"/>
       <c r="AK20" s="5"/>
@@ -7824,7 +7873,10 @@
         <f t="shared" si="8"/>
         <v>73</v>
       </c>
-      <c r="AH21" s="5"/>
+      <c r="AH21" s="5">
+        <f t="shared" si="9"/>
+        <v>13.519</v>
+      </c>
       <c r="AI21" s="5"/>
       <c r="AJ21" s="5"/>
       <c r="AK21" s="5"/>
@@ -7941,7 +7993,10 @@
         <f t="shared" si="8"/>
         <v>66</v>
       </c>
-      <c r="AH22" s="5"/>
+      <c r="AH22" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI22" s="5"/>
       <c r="AJ22" s="5"/>
       <c r="AK22" s="5"/>
@@ -8057,7 +8112,10 @@
         <f t="shared" si="8"/>
         <v>20</v>
       </c>
-      <c r="AH23" s="5"/>
+      <c r="AH23" s="5">
+        <f t="shared" si="9"/>
+        <v>0.77400000000000002</v>
+      </c>
       <c r="AI23" s="5"/>
       <c r="AJ23" s="5"/>
       <c r="AK23" s="5"/>
@@ -8172,7 +8230,10 @@
         <f t="shared" si="8"/>
         <v>48</v>
       </c>
-      <c r="AH24" s="5"/>
+      <c r="AH24" s="5">
+        <f t="shared" si="9"/>
+        <v>5.6917999999999997</v>
+      </c>
       <c r="AI24" s="5"/>
       <c r="AJ24" s="5"/>
       <c r="AK24" s="5"/>
@@ -8284,7 +8345,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="5"/>
+      <c r="AH25" s="5">
+        <f t="shared" si="9"/>
+        <v>0.86399999999999999</v>
+      </c>
       <c r="AI25" s="5"/>
       <c r="AJ25" s="5"/>
       <c r="AK25" s="5"/>
@@ -8398,7 +8462,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="5"/>
+      <c r="AH26" s="5">
+        <f t="shared" si="9"/>
+        <v>0.216</v>
+      </c>
       <c r="AI26" s="5"/>
       <c r="AJ26" s="5"/>
       <c r="AK26" s="5"/>
@@ -8464,7 +8531,7 @@
         <v>86</v>
       </c>
       <c r="R27" s="4">
-        <f t="shared" ref="R27:R30" si="9">S27</f>
+        <f t="shared" ref="R27:R30" si="10">S27</f>
         <v>150</v>
       </c>
       <c r="S27" s="21">
@@ -8516,7 +8583,10 @@
         <f t="shared" si="8"/>
         <v>22.5</v>
       </c>
-      <c r="AH27" s="5"/>
+      <c r="AH27" s="5">
+        <f t="shared" si="9"/>
+        <v>1.5</v>
+      </c>
       <c r="AI27" s="5"/>
       <c r="AJ27" s="5"/>
       <c r="AK27" s="5"/>
@@ -8584,7 +8654,7 @@
         <v>626.29679999999996</v>
       </c>
       <c r="R28" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>800</v>
       </c>
       <c r="S28" s="21">
@@ -8634,7 +8704,10 @@
         <f t="shared" si="8"/>
         <v>800</v>
       </c>
-      <c r="AH28" s="5"/>
+      <c r="AH28" s="5">
+        <f t="shared" si="9"/>
+        <v>72.253399999999999</v>
+      </c>
       <c r="AI28" s="5"/>
       <c r="AJ28" s="5"/>
       <c r="AK28" s="5"/>
@@ -8751,7 +8824,10 @@
         <f t="shared" si="8"/>
         <v>48</v>
       </c>
-      <c r="AH29" s="5"/>
+      <c r="AH29" s="5">
+        <f t="shared" si="9"/>
+        <v>5.5200000000000005</v>
+      </c>
       <c r="AI29" s="5"/>
       <c r="AJ29" s="5"/>
       <c r="AK29" s="5"/>
@@ -8819,7 +8895,7 @@
         <v>380</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>470</v>
       </c>
       <c r="S30" s="21">
@@ -8869,7 +8945,10 @@
         <f t="shared" si="8"/>
         <v>188</v>
       </c>
-      <c r="AH30" s="5"/>
+      <c r="AH30" s="5">
+        <f t="shared" si="9"/>
+        <v>20.240000000000002</v>
+      </c>
       <c r="AI30" s="5"/>
       <c r="AJ30" s="5"/>
       <c r="AK30" s="5"/>
@@ -8975,7 +9054,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="5"/>
+      <c r="AH31" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI31" s="5"/>
       <c r="AJ31" s="5"/>
       <c r="AK31" s="5"/>
@@ -9093,7 +9175,10 @@
         <f t="shared" si="8"/>
         <v>80</v>
       </c>
-      <c r="AH32" s="5"/>
+      <c r="AH32" s="5">
+        <f t="shared" si="9"/>
+        <v>15.680000000000001</v>
+      </c>
       <c r="AI32" s="5"/>
       <c r="AJ32" s="5"/>
       <c r="AK32" s="5"/>
@@ -9197,7 +9282,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="5"/>
+      <c r="AH33" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI33" s="5"/>
       <c r="AJ33" s="5"/>
       <c r="AK33" s="5"/>
@@ -9311,7 +9399,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="5"/>
+      <c r="AH34" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI34" s="5"/>
       <c r="AJ34" s="5"/>
       <c r="AK34" s="5"/>
@@ -9375,7 +9466,7 @@
         <v>5.3666</v>
       </c>
       <c r="Q35" s="4">
-        <f t="shared" ref="Q35:Q42" si="10">15*P35-O35-F35</f>
+        <f t="shared" ref="Q35:Q42" si="11">15*P35-O35-F35</f>
         <v>11.461999999999989</v>
       </c>
       <c r="R35" s="4">
@@ -9428,7 +9519,10 @@
         <f t="shared" si="8"/>
         <v>11</v>
       </c>
-      <c r="AH35" s="5"/>
+      <c r="AH35" s="5">
+        <f t="shared" si="9"/>
+        <v>5.3666</v>
+      </c>
       <c r="AI35" s="5"/>
       <c r="AJ35" s="5"/>
       <c r="AK35" s="5"/>
@@ -9492,7 +9586,7 @@
         <v>10.1844</v>
       </c>
       <c r="Q36" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>42.141999999999996</v>
       </c>
       <c r="R36" s="4">
@@ -9545,7 +9639,10 @@
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
-      <c r="AH36" s="5"/>
+      <c r="AH36" s="5">
+        <f t="shared" si="9"/>
+        <v>10.1844</v>
+      </c>
       <c r="AI36" s="5"/>
       <c r="AJ36" s="5"/>
       <c r="AK36" s="5"/>
@@ -9659,7 +9756,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="5"/>
+      <c r="AH37" s="5">
+        <f t="shared" si="9"/>
+        <v>10.182599999999999</v>
+      </c>
       <c r="AI37" s="5"/>
       <c r="AJ37" s="5"/>
       <c r="AK37" s="5"/>
@@ -9710,7 +9810,7 @@
         <v>32</v>
       </c>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:L69" si="11">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="12">E38-K38</f>
         <v>-1.8170000000000002</v>
       </c>
       <c r="M38" s="5"/>
@@ -9719,11 +9819,11 @@
         <v>13</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" ref="P38:P69" si="12">E38/5</f>
+        <f t="shared" ref="P38:P69" si="13">E38/5</f>
         <v>6.0366</v>
       </c>
       <c r="Q38" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>37.297000000000004</v>
       </c>
       <c r="R38" s="4">
@@ -9736,7 +9836,7 @@
         <v>14.95080011927244</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" ref="U38:U69" si="13">(F38+O38)/P38</f>
+        <f t="shared" ref="U38:U69" si="14">(F38+O38)/P38</f>
         <v>8.8215220488354369</v>
       </c>
       <c r="V38" s="5">
@@ -9774,7 +9874,10 @@
         <f t="shared" si="8"/>
         <v>37</v>
       </c>
-      <c r="AH38" s="5"/>
+      <c r="AH38" s="5">
+        <f t="shared" si="9"/>
+        <v>6.0366</v>
+      </c>
       <c r="AI38" s="5"/>
       <c r="AJ38" s="5"/>
       <c r="AK38" s="5"/>
@@ -9825,7 +9928,7 @@
         <v>319</v>
       </c>
       <c r="L39" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4</v>
       </c>
       <c r="M39" s="5"/>
@@ -9834,7 +9937,7 @@
         <v>52</v>
       </c>
       <c r="P39" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>64.599999999999994</v>
       </c>
       <c r="Q39" s="4">
@@ -9842,7 +9945,7 @@
         <v>579.39999999999986</v>
       </c>
       <c r="R39" s="4">
-        <f t="shared" ref="R39:R40" si="14">S39</f>
+        <f t="shared" ref="R39:R40" si="15">S39</f>
         <v>700</v>
       </c>
       <c r="S39" s="21">
@@ -9854,7 +9957,7 @@
         <v>15.866873065015481</v>
       </c>
       <c r="U39" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.0309597523219818</v>
       </c>
       <c r="V39" s="5">
@@ -9892,7 +9995,10 @@
         <f t="shared" si="8"/>
         <v>210</v>
       </c>
-      <c r="AH39" s="5"/>
+      <c r="AH39" s="5">
+        <f t="shared" si="9"/>
+        <v>19.38</v>
+      </c>
       <c r="AI39" s="5"/>
       <c r="AJ39" s="5"/>
       <c r="AK39" s="5"/>
@@ -9943,7 +10049,7 @@
         <v>141.102</v>
       </c>
       <c r="L40" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>19.304000000000002</v>
       </c>
       <c r="M40" s="5"/>
@@ -9952,7 +10058,7 @@
         <v>0</v>
       </c>
       <c r="P40" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>32.081200000000003</v>
       </c>
       <c r="Q40" s="4">
@@ -9960,7 +10066,7 @@
         <v>290.06680000000006</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>380</v>
       </c>
       <c r="S40" s="21">
@@ -9972,7 +10078,7 @@
         <v>16.803299128461525</v>
       </c>
       <c r="U40" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.9583556724810789</v>
       </c>
       <c r="V40" s="5">
@@ -10012,7 +10118,10 @@
         <f t="shared" si="8"/>
         <v>380</v>
       </c>
-      <c r="AH40" s="5"/>
+      <c r="AH40" s="5">
+        <f t="shared" si="9"/>
+        <v>32.081200000000003</v>
+      </c>
       <c r="AI40" s="5"/>
       <c r="AJ40" s="5"/>
       <c r="AK40" s="5"/>
@@ -10063,7 +10172,7 @@
         <v>33</v>
       </c>
       <c r="L41" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.5499999999999972</v>
       </c>
       <c r="M41" s="5"/>
@@ -10072,11 +10181,11 @@
         <v>0</v>
       </c>
       <c r="P41" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.1099999999999994</v>
       </c>
       <c r="Q41" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>57.209999999999994</v>
       </c>
       <c r="R41" s="4">
@@ -10089,7 +10198,7 @@
         <v>14.970464135021098</v>
       </c>
       <c r="U41" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.9535864978902957</v>
       </c>
       <c r="V41" s="5">
@@ -10127,7 +10236,10 @@
         <f t="shared" si="8"/>
         <v>57</v>
       </c>
-      <c r="AH41" s="5"/>
+      <c r="AH41" s="5">
+        <f t="shared" si="9"/>
+        <v>7.1099999999999994</v>
+      </c>
       <c r="AI41" s="5"/>
       <c r="AJ41" s="5"/>
       <c r="AK41" s="5"/>
@@ -10178,7 +10290,7 @@
         <v>436</v>
       </c>
       <c r="L42" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2</v>
       </c>
       <c r="M42" s="5"/>
@@ -10187,11 +10299,11 @@
         <v>700</v>
       </c>
       <c r="P42" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>87.6</v>
       </c>
       <c r="Q42" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>609</v>
       </c>
       <c r="R42" s="4">
@@ -10207,7 +10319,7 @@
         <v>16.038812785388128</v>
       </c>
       <c r="U42" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>8.0479452054794525</v>
       </c>
       <c r="V42" s="5">
@@ -10245,7 +10357,10 @@
         <f t="shared" si="8"/>
         <v>244.99999999999997</v>
       </c>
-      <c r="AH42" s="5"/>
+      <c r="AH42" s="5">
+        <f t="shared" si="9"/>
+        <v>30.659999999999997</v>
+      </c>
       <c r="AI42" s="5"/>
       <c r="AJ42" s="5"/>
       <c r="AK42" s="5"/>
@@ -10298,7 +10413,7 @@
         <v>142</v>
       </c>
       <c r="L43" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-161</v>
       </c>
       <c r="M43" s="13"/>
@@ -10307,7 +10422,7 @@
         <v>0</v>
       </c>
       <c r="P43" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>-3.8</v>
       </c>
       <c r="Q43" s="15"/>
@@ -10321,7 +10436,7 @@
         <v>0.78947368421052633</v>
       </c>
       <c r="U43" s="13">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0.78947368421052633</v>
       </c>
       <c r="V43" s="13">
@@ -10361,7 +10476,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH43" s="5"/>
+      <c r="AH43" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI43" s="5"/>
       <c r="AJ43" s="5"/>
       <c r="AK43" s="5"/>
@@ -10412,7 +10530,7 @@
         <v>115</v>
       </c>
       <c r="L44" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="M44" s="5"/>
@@ -10421,7 +10539,7 @@
         <v>137</v>
       </c>
       <c r="P44" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>22.8</v>
       </c>
       <c r="Q44" s="4">
@@ -10441,7 +10559,7 @@
         <v>20</v>
       </c>
       <c r="U44" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>9.0350877192982448</v>
       </c>
       <c r="V44" s="5">
@@ -10479,7 +10597,10 @@
         <f t="shared" si="8"/>
         <v>102.5</v>
       </c>
-      <c r="AH44" s="5"/>
+      <c r="AH44" s="5">
+        <f t="shared" si="9"/>
+        <v>9.347999999999999</v>
+      </c>
       <c r="AI44" s="5"/>
       <c r="AJ44" s="5"/>
       <c r="AK44" s="5"/>
@@ -10524,7 +10645,7 @@
       <c r="J45" s="13"/>
       <c r="K45" s="13"/>
       <c r="L45" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M45" s="13"/>
@@ -10533,7 +10654,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Q45" s="15"/>
@@ -10547,7 +10668,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U45" s="13" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V45" s="13">
@@ -10587,7 +10708,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH45" s="5"/>
+      <c r="AH45" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI45" s="5"/>
       <c r="AJ45" s="5"/>
       <c r="AK45" s="5"/>
@@ -10630,7 +10754,7 @@
       <c r="J46" s="9"/>
       <c r="K46" s="9"/>
       <c r="L46" s="9">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M46" s="9"/>
@@ -10639,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="P46" s="9">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Q46" s="11"/>
@@ -10653,7 +10777,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U46" s="9" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V46" s="9">
@@ -10691,7 +10815,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="5"/>
+      <c r="AH46" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI46" s="5"/>
       <c r="AJ46" s="5"/>
       <c r="AK46" s="5"/>
@@ -10742,7 +10869,7 @@
         <v>96</v>
       </c>
       <c r="L47" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="M47" s="5"/>
@@ -10751,7 +10878,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>19</v>
       </c>
       <c r="Q47" s="4">
@@ -10770,7 +10897,7 @@
         <v>13.894736842105264</v>
       </c>
       <c r="U47" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3157894736842106</v>
       </c>
       <c r="V47" s="5">
@@ -10810,7 +10937,10 @@
         <f t="shared" si="8"/>
         <v>79.2</v>
       </c>
-      <c r="AH47" s="5"/>
+      <c r="AH47" s="5">
+        <f t="shared" si="9"/>
+        <v>6.84</v>
+      </c>
       <c r="AI47" s="5"/>
       <c r="AJ47" s="5"/>
       <c r="AK47" s="5"/>
@@ -10861,7 +10991,7 @@
         <v>54</v>
       </c>
       <c r="L48" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="M48" s="5"/>
@@ -10870,7 +11000,7 @@
         <v>80</v>
       </c>
       <c r="P48" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.6</v>
       </c>
       <c r="Q48" s="4">
@@ -10886,7 +11016,7 @@
         <v>15.566037735849058</v>
       </c>
       <c r="U48" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>14.811320754716983</v>
       </c>
       <c r="V48" s="5">
@@ -10926,7 +11056,10 @@
         <f t="shared" si="8"/>
         <v>2.64</v>
       </c>
-      <c r="AH48" s="5"/>
+      <c r="AH48" s="5">
+        <f t="shared" si="9"/>
+        <v>3.4980000000000002</v>
+      </c>
       <c r="AI48" s="5"/>
       <c r="AJ48" s="5"/>
       <c r="AK48" s="5"/>
@@ -10977,7 +11110,7 @@
         <v>82</v>
       </c>
       <c r="L49" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-27</v>
       </c>
       <c r="M49" s="5"/>
@@ -10986,7 +11119,7 @@
         <v>180</v>
       </c>
       <c r="P49" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>11</v>
       </c>
       <c r="Q49" s="4"/>
@@ -11003,7 +11136,7 @@
         <v>31.272727272727273</v>
       </c>
       <c r="U49" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>22.181818181818183</v>
       </c>
       <c r="V49" s="5">
@@ -11041,7 +11174,10 @@
         <f t="shared" si="8"/>
         <v>40</v>
       </c>
-      <c r="AH49" s="5"/>
+      <c r="AH49" s="5">
+        <f t="shared" si="9"/>
+        <v>4.4000000000000004</v>
+      </c>
       <c r="AI49" s="5"/>
       <c r="AJ49" s="5"/>
       <c r="AK49" s="5"/>
@@ -11090,7 +11226,7 @@
         <v>9</v>
       </c>
       <c r="L50" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-1</v>
       </c>
       <c r="M50" s="5"/>
@@ -11099,11 +11235,11 @@
         <v>16</v>
       </c>
       <c r="P50" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.6</v>
       </c>
       <c r="Q50" s="4">
-        <f t="shared" ref="Q50:Q66" si="15">15*P50-O50-F50</f>
+        <f t="shared" ref="Q50:Q66" si="16">15*P50-O50-F50</f>
         <v>8</v>
       </c>
       <c r="R50" s="4">
@@ -11116,7 +11252,7 @@
         <v>15</v>
       </c>
       <c r="U50" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10</v>
       </c>
       <c r="V50" s="5">
@@ -11156,7 +11292,10 @@
         <f t="shared" si="8"/>
         <v>2.64</v>
       </c>
-      <c r="AH50" s="5"/>
+      <c r="AH50" s="5">
+        <f t="shared" si="9"/>
+        <v>0.52800000000000002</v>
+      </c>
       <c r="AI50" s="5"/>
       <c r="AJ50" s="5"/>
       <c r="AK50" s="5"/>
@@ -11207,7 +11346,7 @@
         <v>298.5</v>
       </c>
       <c r="L51" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>8.2719999999999914</v>
       </c>
       <c r="M51" s="5"/>
@@ -11216,7 +11355,7 @@
         <v>250</v>
       </c>
       <c r="P51" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>61.354399999999998</v>
       </c>
       <c r="Q51" s="4">
@@ -11236,7 +11375,7 @@
         <v>15.914930306546882</v>
       </c>
       <c r="U51" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.1356805705866249</v>
       </c>
       <c r="V51" s="5">
@@ -11274,7 +11413,10 @@
         <f t="shared" si="8"/>
         <v>600</v>
       </c>
-      <c r="AH51" s="5"/>
+      <c r="AH51" s="5">
+        <f t="shared" si="9"/>
+        <v>61.354399999999998</v>
+      </c>
       <c r="AI51" s="5"/>
       <c r="AJ51" s="5"/>
       <c r="AK51" s="5"/>
@@ -11325,7 +11467,7 @@
         <v>41</v>
       </c>
       <c r="L52" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-2</v>
       </c>
       <c r="M52" s="5"/>
@@ -11334,11 +11476,11 @@
         <v>0</v>
       </c>
       <c r="P52" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.8</v>
       </c>
       <c r="Q52" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>19</v>
       </c>
       <c r="R52" s="4">
@@ -11351,7 +11493,7 @@
         <v>15</v>
       </c>
       <c r="U52" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.564102564102564</v>
       </c>
       <c r="V52" s="5">
@@ -11391,7 +11533,10 @@
         <f t="shared" si="8"/>
         <v>7.6000000000000005</v>
       </c>
-      <c r="AH52" s="5"/>
+      <c r="AH52" s="5">
+        <f t="shared" si="9"/>
+        <v>3.12</v>
+      </c>
       <c r="AI52" s="5"/>
       <c r="AJ52" s="5"/>
       <c r="AK52" s="5"/>
@@ -11440,7 +11585,7 @@
         <v>13.3</v>
       </c>
       <c r="L53" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-0.21900000000000119</v>
       </c>
       <c r="M53" s="5"/>
@@ -11449,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="P53" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.6162000000000001</v>
       </c>
       <c r="Q53" s="4"/>
@@ -11463,7 +11608,7 @@
         <v>66.577478786025537</v>
       </c>
       <c r="U53" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>66.577478786025537</v>
       </c>
       <c r="V53" s="5">
@@ -11503,7 +11648,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="5"/>
+      <c r="AH53" s="5">
+        <f t="shared" si="9"/>
+        <v>2.6162000000000001</v>
+      </c>
       <c r="AI53" s="5"/>
       <c r="AJ53" s="5"/>
       <c r="AK53" s="5"/>
@@ -11554,7 +11702,7 @@
         <v>32</v>
       </c>
       <c r="L54" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>4.1460000000000008</v>
       </c>
       <c r="M54" s="5"/>
@@ -11563,7 +11711,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.2292000000000005</v>
       </c>
       <c r="Q54" s="4"/>
@@ -11577,7 +11725,7 @@
         <v>15.620262269684057</v>
       </c>
       <c r="U54" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.620262269684057</v>
       </c>
       <c r="V54" s="5">
@@ -11617,7 +11765,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="5"/>
+      <c r="AH54" s="5">
+        <f t="shared" si="9"/>
+        <v>7.2292000000000005</v>
+      </c>
       <c r="AI54" s="5"/>
       <c r="AJ54" s="5"/>
       <c r="AK54" s="5"/>
@@ -11668,7 +11819,7 @@
         <v>21</v>
       </c>
       <c r="L55" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M55" s="5"/>
@@ -11677,7 +11828,7 @@
         <v>60</v>
       </c>
       <c r="P55" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.2</v>
       </c>
       <c r="Q55" s="4"/>
@@ -11691,7 +11842,7 @@
         <v>20</v>
       </c>
       <c r="U55" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>20</v>
       </c>
       <c r="V55" s="5">
@@ -11729,7 +11880,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH55" s="5"/>
+      <c r="AH55" s="5">
+        <f t="shared" si="9"/>
+        <v>1.05</v>
+      </c>
       <c r="AI55" s="5"/>
       <c r="AJ55" s="5"/>
       <c r="AK55" s="5"/>
@@ -11780,7 +11934,7 @@
         <v>18.100000000000001</v>
       </c>
       <c r="L56" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.68599999999999994</v>
       </c>
       <c r="M56" s="5"/>
@@ -11789,7 +11943,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>3.7572000000000001</v>
       </c>
       <c r="Q56" s="4">
@@ -11808,7 +11962,7 @@
         <v>16.601192377302247</v>
       </c>
       <c r="U56" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>3.2934099861599062</v>
       </c>
       <c r="V56" s="5">
@@ -11846,7 +12000,10 @@
         <f t="shared" si="8"/>
         <v>50</v>
       </c>
-      <c r="AH56" s="5"/>
+      <c r="AH56" s="5">
+        <f t="shared" si="9"/>
+        <v>3.7572000000000001</v>
+      </c>
       <c r="AI56" s="5"/>
       <c r="AJ56" s="5"/>
       <c r="AK56" s="5"/>
@@ -11897,7 +12054,7 @@
         <v>109</v>
       </c>
       <c r="L57" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M57" s="5"/>
@@ -11906,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="P57" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21</v>
       </c>
       <c r="Q57" s="4"/>
@@ -11920,7 +12077,7 @@
         <v>15.761904761904763</v>
       </c>
       <c r="U57" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>15.761904761904763</v>
       </c>
       <c r="V57" s="5">
@@ -11958,7 +12115,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH57" s="5"/>
+      <c r="AH57" s="5">
+        <f t="shared" si="9"/>
+        <v>5.67</v>
+      </c>
       <c r="AI57" s="5"/>
       <c r="AJ57" s="5"/>
       <c r="AK57" s="5"/>
@@ -12009,7 +12169,7 @@
         <v>103</v>
       </c>
       <c r="L58" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M58" s="5"/>
@@ -12018,15 +12178,15 @@
         <v>64</v>
       </c>
       <c r="P58" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>20.6</v>
       </c>
       <c r="Q58" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>185</v>
       </c>
       <c r="R58" s="4">
-        <f t="shared" ref="R58:R60" si="16">S58</f>
+        <f t="shared" ref="R58:R60" si="17">S58</f>
         <v>250</v>
       </c>
       <c r="S58" s="21">
@@ -12038,7 +12198,7 @@
         <v>18.155339805825243</v>
       </c>
       <c r="U58" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.0194174757281553</v>
       </c>
       <c r="V58" s="5">
@@ -12076,7 +12236,10 @@
         <f t="shared" si="8"/>
         <v>75</v>
       </c>
-      <c r="AH58" s="5"/>
+      <c r="AH58" s="5">
+        <f t="shared" si="9"/>
+        <v>6.1800000000000006</v>
+      </c>
       <c r="AI58" s="5"/>
       <c r="AJ58" s="5"/>
       <c r="AK58" s="5"/>
@@ -12127,7 +12290,7 @@
         <v>438</v>
       </c>
       <c r="L59" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-13</v>
       </c>
       <c r="M59" s="5"/>
@@ -12136,15 +12299,15 @@
         <v>209</v>
       </c>
       <c r="P59" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>85</v>
       </c>
       <c r="Q59" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>375</v>
       </c>
       <c r="R59" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>500</v>
       </c>
       <c r="S59" s="21">
@@ -12156,7 +12319,7 @@
         <v>16.470588235294116</v>
       </c>
       <c r="U59" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>10.588235294117647</v>
       </c>
       <c r="V59" s="5">
@@ -12194,7 +12357,10 @@
         <f t="shared" si="8"/>
         <v>205</v>
       </c>
-      <c r="AH59" s="5"/>
+      <c r="AH59" s="5">
+        <f t="shared" si="9"/>
+        <v>34.85</v>
+      </c>
       <c r="AI59" s="5"/>
       <c r="AJ59" s="5"/>
       <c r="AK59" s="5"/>
@@ -12245,7 +12411,7 @@
         <v>105.2</v>
       </c>
       <c r="L60" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.203000000000003</v>
       </c>
       <c r="M60" s="5"/>
@@ -12254,15 +12420,15 @@
         <v>85</v>
       </c>
       <c r="P60" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>21.2806</v>
       </c>
       <c r="Q60" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>198.41900000000001</v>
       </c>
       <c r="R60" s="4">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>300</v>
       </c>
       <c r="S60" s="21">
@@ -12274,7 +12440,7 @@
         <v>19.773408644493106</v>
       </c>
       <c r="U60" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.6760617651757936</v>
       </c>
       <c r="V60" s="5">
@@ -12312,7 +12478,10 @@
         <f t="shared" si="8"/>
         <v>300</v>
       </c>
-      <c r="AH60" s="5"/>
+      <c r="AH60" s="5">
+        <f t="shared" si="9"/>
+        <v>21.2806</v>
+      </c>
       <c r="AI60" s="5"/>
       <c r="AJ60" s="5"/>
       <c r="AK60" s="5"/>
@@ -12363,7 +12532,7 @@
         <v>56</v>
       </c>
       <c r="L61" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M61" s="5"/>
@@ -12372,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>10.4</v>
       </c>
       <c r="Q61" s="4"/>
@@ -12386,7 +12555,7 @@
         <v>38.46153846153846</v>
       </c>
       <c r="U61" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>38.46153846153846</v>
       </c>
       <c r="V61" s="5">
@@ -12426,7 +12595,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="5"/>
+      <c r="AH61" s="5">
+        <f t="shared" si="9"/>
+        <v>3.6399999999999997</v>
+      </c>
       <c r="AI61" s="5"/>
       <c r="AJ61" s="5"/>
       <c r="AK61" s="5"/>
@@ -12477,7 +12649,7 @@
         <v>12</v>
       </c>
       <c r="L62" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.8079999999999998</v>
       </c>
       <c r="M62" s="5"/>
@@ -12486,11 +12658,11 @@
         <v>15</v>
       </c>
       <c r="P62" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.7616000000000001</v>
       </c>
       <c r="Q62" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>6.0189999999999984</v>
       </c>
       <c r="R62" s="4">
@@ -12503,7 +12675,7 @@
         <v>14.993119930475087</v>
       </c>
       <c r="U62" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>12.820466396292005</v>
       </c>
       <c r="V62" s="5">
@@ -12541,7 +12713,10 @@
         <f t="shared" si="8"/>
         <v>6</v>
       </c>
-      <c r="AH62" s="5"/>
+      <c r="AH62" s="5">
+        <f t="shared" si="9"/>
+        <v>2.7616000000000001</v>
+      </c>
       <c r="AI62" s="5"/>
       <c r="AJ62" s="5"/>
       <c r="AK62" s="5"/>
@@ -12592,7 +12767,7 @@
         <v>328</v>
       </c>
       <c r="L63" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-4</v>
       </c>
       <c r="M63" s="5"/>
@@ -12601,11 +12776,11 @@
         <v>200</v>
       </c>
       <c r="P63" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>64.8</v>
       </c>
       <c r="Q63" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>500</v>
       </c>
       <c r="R63" s="4">
@@ -12618,7 +12793,7 @@
         <v>15</v>
       </c>
       <c r="U63" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.283950617283951</v>
       </c>
       <c r="V63" s="5">
@@ -12656,7 +12831,10 @@
         <f t="shared" si="8"/>
         <v>205</v>
       </c>
-      <c r="AH63" s="5"/>
+      <c r="AH63" s="5">
+        <f t="shared" si="9"/>
+        <v>26.567999999999998</v>
+      </c>
       <c r="AI63" s="5"/>
       <c r="AJ63" s="5"/>
       <c r="AK63" s="5"/>
@@ -12705,7 +12883,7 @@
         <v>123.7</v>
       </c>
       <c r="L64" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-47.403000000000006</v>
       </c>
       <c r="M64" s="5"/>
@@ -12714,11 +12892,11 @@
         <v>100</v>
       </c>
       <c r="P64" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>15.259399999999999</v>
       </c>
       <c r="Q64" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>128.89099999999999</v>
       </c>
       <c r="R64" s="4">
@@ -12733,7 +12911,7 @@
         <v>20.970680367511175</v>
       </c>
       <c r="U64" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>6.5533376148472415</v>
       </c>
       <c r="V64" s="5">
@@ -12771,7 +12949,10 @@
         <f t="shared" si="8"/>
         <v>220</v>
       </c>
-      <c r="AH64" s="5"/>
+      <c r="AH64" s="5">
+        <f t="shared" si="9"/>
+        <v>15.259399999999999</v>
+      </c>
       <c r="AI64" s="5"/>
       <c r="AJ64" s="5"/>
       <c r="AK64" s="5"/>
@@ -12822,7 +13003,7 @@
         <v>130</v>
       </c>
       <c r="L65" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-11</v>
       </c>
       <c r="M65" s="5"/>
@@ -12831,15 +13012,15 @@
         <v>184</v>
       </c>
       <c r="P65" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>23.8</v>
       </c>
       <c r="Q65" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>170</v>
       </c>
       <c r="R65" s="4">
-        <f t="shared" ref="R65" si="17">S65</f>
+        <f t="shared" ref="R65" si="18">S65</f>
         <v>300</v>
       </c>
       <c r="S65" s="21">
@@ -12851,7 +13032,7 @@
         <v>20.462184873949578</v>
       </c>
       <c r="U65" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.8571428571428568</v>
       </c>
       <c r="V65" s="5">
@@ -12889,7 +13070,10 @@
         <f t="shared" si="8"/>
         <v>90</v>
       </c>
-      <c r="AH65" s="5"/>
+      <c r="AH65" s="5">
+        <f t="shared" si="9"/>
+        <v>7.14</v>
+      </c>
       <c r="AI65" s="5"/>
       <c r="AJ65" s="5"/>
       <c r="AK65" s="5"/>
@@ -12940,7 +13124,7 @@
         <v>86</v>
       </c>
       <c r="L66" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>-3</v>
       </c>
       <c r="M66" s="5"/>
@@ -12949,11 +13133,11 @@
         <v>0</v>
       </c>
       <c r="P66" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>16.600000000000001</v>
       </c>
       <c r="Q66" s="4">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>150.00000000000003</v>
       </c>
       <c r="R66" s="4">
@@ -12968,7 +13152,7 @@
         <v>21.024096385542165</v>
       </c>
       <c r="U66" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.9638554216867465</v>
       </c>
       <c r="V66" s="5">
@@ -13006,7 +13190,10 @@
         <f t="shared" si="8"/>
         <v>45</v>
       </c>
-      <c r="AH66" s="5"/>
+      <c r="AH66" s="5">
+        <f t="shared" si="9"/>
+        <v>2.988</v>
+      </c>
       <c r="AI66" s="5"/>
       <c r="AJ66" s="5"/>
       <c r="AK66" s="5"/>
@@ -13055,7 +13242,7 @@
         <v>12</v>
       </c>
       <c r="L67" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M67" s="5"/>
@@ -13064,7 +13251,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.4</v>
       </c>
       <c r="Q67" s="4"/>
@@ -13078,7 +13265,7 @@
         <v>26.666666666666668</v>
       </c>
       <c r="U67" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>26.666666666666668</v>
       </c>
       <c r="V67" s="5">
@@ -13118,7 +13305,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH67" s="5"/>
+      <c r="AH67" s="5">
+        <f t="shared" si="9"/>
+        <v>0.52800000000000002</v>
+      </c>
       <c r="AI67" s="5"/>
       <c r="AJ67" s="5"/>
       <c r="AK67" s="5"/>
@@ -13157,7 +13347,7 @@
       <c r="J68" s="13"/>
       <c r="K68" s="13"/>
       <c r="L68" s="13">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M68" s="13"/>
@@ -13166,7 +13356,7 @@
         <v>0</v>
       </c>
       <c r="P68" s="13">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="Q68" s="15"/>
@@ -13180,7 +13370,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U68" s="13" t="e">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V68" s="13">
@@ -13220,7 +13410,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH68" s="5"/>
+      <c r="AH68" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI68" s="5"/>
       <c r="AJ68" s="5"/>
       <c r="AK68" s="5"/>
@@ -13272,7 +13465,7 @@
         <v>303</v>
       </c>
       <c r="L69" s="5">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
       <c r="M69" s="5"/>
@@ -13281,7 +13474,7 @@
         <v>230</v>
       </c>
       <c r="P69" s="5">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>60.8</v>
       </c>
       <c r="Q69" s="4">
@@ -13298,7 +13491,7 @@
         <v>13.996710526315789</v>
       </c>
       <c r="U69" s="5">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.1644736842105265</v>
       </c>
       <c r="V69" s="5">
@@ -13336,7 +13529,10 @@
         <f t="shared" si="8"/>
         <v>187.95</v>
       </c>
-      <c r="AH69" s="5"/>
+      <c r="AH69" s="5">
+        <f t="shared" si="9"/>
+        <v>21.279999999999998</v>
+      </c>
       <c r="AI69" s="5"/>
       <c r="AJ69" s="5"/>
       <c r="AK69" s="5"/>
@@ -13375,7 +13571,7 @@
       <c r="J70" s="13"/>
       <c r="K70" s="13"/>
       <c r="L70" s="13">
-        <f t="shared" ref="L70:L101" si="18">E70-K70</f>
+        <f t="shared" ref="L70:L101" si="19">E70-K70</f>
         <v>0</v>
       </c>
       <c r="M70" s="13"/>
@@ -13384,7 +13580,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="13">
-        <f t="shared" ref="P70:P101" si="19">E70/5</f>
+        <f t="shared" ref="P70:P101" si="20">E70/5</f>
         <v>0</v>
       </c>
       <c r="Q70" s="15"/>
@@ -13398,7 +13594,7 @@
         <v>#DIV/0!</v>
       </c>
       <c r="U70" s="13" t="e">
-        <f t="shared" ref="U70:U101" si="20">(F70+O70)/P70</f>
+        <f t="shared" ref="U70:U101" si="21">(F70+O70)/P70</f>
         <v>#DIV/0!</v>
       </c>
       <c r="V70" s="13">
@@ -13438,7 +13634,10 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AH70" s="5"/>
+      <c r="AH70" s="5">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
       <c r="AI70" s="5"/>
       <c r="AJ70" s="5"/>
       <c r="AK70" s="5"/>
@@ -13489,7 +13688,7 @@
         <v>98.9</v>
       </c>
       <c r="L71" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3.3259999999999934</v>
       </c>
       <c r="M71" s="5"/>
@@ -13498,11 +13697,11 @@
         <v>145</v>
       </c>
       <c r="P71" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>20.4452</v>
       </c>
       <c r="Q71" s="4">
-        <f t="shared" ref="Q71:Q84" si="21">15*P71-O71-F71</f>
+        <f t="shared" ref="Q71:Q84" si="22">15*P71-O71-F71</f>
         <v>100.256</v>
       </c>
       <c r="R71" s="4">
@@ -13514,11 +13713,11 @@
         <v>200</v>
       </c>
       <c r="T71" s="5">
-        <f t="shared" ref="T71:T109" si="22">(F71+O71+R71)/P71</f>
+        <f t="shared" ref="T71:T109" si="23">(F71+O71+R71)/P71</f>
         <v>19.878602312523235</v>
       </c>
       <c r="U71" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>10.096355134701543</v>
       </c>
       <c r="V71" s="5">
@@ -13553,10 +13752,13 @@
       </c>
       <c r="AF71" s="5"/>
       <c r="AG71" s="5">
-        <f t="shared" ref="AG71:AG109" si="23">G71*R71</f>
+        <f t="shared" ref="AG71:AG109" si="24">G71*R71</f>
         <v>200</v>
       </c>
-      <c r="AH71" s="5"/>
+      <c r="AH71" s="5">
+        <f t="shared" ref="AH71:AH109" si="25">P71*G71</f>
+        <v>20.4452</v>
+      </c>
       <c r="AI71" s="5"/>
       <c r="AJ71" s="5"/>
       <c r="AK71" s="5"/>
@@ -13607,7 +13809,7 @@
         <v>181.4</v>
       </c>
       <c r="L72" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>10.960999999999984</v>
       </c>
       <c r="M72" s="5"/>
@@ -13616,24 +13818,24 @@
         <v>300</v>
       </c>
       <c r="P72" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>38.472200000000001</v>
       </c>
       <c r="Q72" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>224.38099999999997</v>
       </c>
       <c r="R72" s="4">
-        <f t="shared" ref="R72:R109" si="24">ROUND(Q72,0)</f>
+        <f t="shared" ref="R72:R109" si="26">ROUND(Q72,0)</f>
         <v>224</v>
       </c>
       <c r="S72" s="21"/>
       <c r="T72" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>14.990096745182235</v>
       </c>
       <c r="U72" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.1677107105910238</v>
       </c>
       <c r="V72" s="5">
@@ -13668,10 +13870,13 @@
       </c>
       <c r="AF72" s="5"/>
       <c r="AG72" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>224</v>
       </c>
-      <c r="AH72" s="5"/>
+      <c r="AH72" s="5">
+        <f t="shared" si="25"/>
+        <v>38.472200000000001</v>
+      </c>
       <c r="AI72" s="5"/>
       <c r="AJ72" s="5"/>
       <c r="AK72" s="5"/>
@@ -13722,7 +13927,7 @@
         <v>352</v>
       </c>
       <c r="L73" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M73" s="5"/>
@@ -13731,24 +13936,24 @@
         <v>150</v>
       </c>
       <c r="P73" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>69.8</v>
       </c>
       <c r="Q73" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>662</v>
       </c>
       <c r="R73" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>662</v>
       </c>
       <c r="S73" s="21"/>
       <c r="T73" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
       <c r="U73" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>5.5157593123209168</v>
       </c>
       <c r="V73" s="5">
@@ -13783,10 +13988,13 @@
       </c>
       <c r="AF73" s="5"/>
       <c r="AG73" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>231.7</v>
       </c>
-      <c r="AH73" s="5"/>
+      <c r="AH73" s="5">
+        <f t="shared" si="25"/>
+        <v>24.429999999999996</v>
+      </c>
       <c r="AI73" s="5"/>
       <c r="AJ73" s="5"/>
       <c r="AK73" s="5"/>
@@ -13837,7 +14045,7 @@
         <v>145</v>
       </c>
       <c r="L74" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M74" s="5"/>
@@ -13846,24 +14054,24 @@
         <v>86</v>
       </c>
       <c r="P74" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>28.8</v>
       </c>
       <c r="Q74" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>233</v>
       </c>
       <c r="R74" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>233</v>
       </c>
       <c r="S74" s="21"/>
       <c r="T74" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
       <c r="U74" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.9097222222222223</v>
       </c>
       <c r="V74" s="5">
@@ -13898,10 +14106,13 @@
       </c>
       <c r="AF74" s="5"/>
       <c r="AG74" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>69.899999999999991</v>
       </c>
-      <c r="AH74" s="5"/>
+      <c r="AH74" s="5">
+        <f t="shared" si="25"/>
+        <v>8.64</v>
+      </c>
       <c r="AI74" s="5"/>
       <c r="AJ74" s="5"/>
       <c r="AK74" s="5"/>
@@ -13952,7 +14163,7 @@
         <v>55</v>
       </c>
       <c r="L75" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M75" s="5"/>
@@ -13961,7 +14172,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>10.8</v>
       </c>
       <c r="Q75" s="4">
@@ -13969,16 +14180,16 @@
         <v>99</v>
       </c>
       <c r="R75" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>99</v>
       </c>
       <c r="S75" s="21"/>
       <c r="T75" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10</v>
       </c>
       <c r="U75" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0.83333333333333326</v>
       </c>
       <c r="V75" s="5">
@@ -14013,10 +14224,13 @@
       </c>
       <c r="AF75" s="5"/>
       <c r="AG75" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>29.7</v>
       </c>
-      <c r="AH75" s="5"/>
+      <c r="AH75" s="5">
+        <f t="shared" si="25"/>
+        <v>3.24</v>
+      </c>
       <c r="AI75" s="5"/>
       <c r="AJ75" s="5"/>
       <c r="AK75" s="5"/>
@@ -14067,7 +14281,7 @@
         <v>280</v>
       </c>
       <c r="L76" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>3</v>
       </c>
       <c r="M76" s="5"/>
@@ -14076,7 +14290,7 @@
         <v>0</v>
       </c>
       <c r="P76" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>56.6</v>
       </c>
       <c r="Q76" s="4">
@@ -14084,16 +14298,16 @@
         <v>524.6</v>
       </c>
       <c r="R76" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>525</v>
       </c>
       <c r="S76" s="21"/>
       <c r="T76" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>11.007067137809187</v>
       </c>
       <c r="U76" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>1.7314487632508833</v>
       </c>
       <c r="V76" s="5">
@@ -14128,10 +14342,13 @@
       </c>
       <c r="AF76" s="5"/>
       <c r="AG76" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>147</v>
       </c>
-      <c r="AH76" s="5"/>
+      <c r="AH76" s="5">
+        <f t="shared" si="25"/>
+        <v>15.848000000000003</v>
+      </c>
       <c r="AI76" s="5"/>
       <c r="AJ76" s="5"/>
       <c r="AK76" s="5"/>
@@ -14182,7 +14399,7 @@
         <v>232</v>
       </c>
       <c r="L77" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M77" s="5"/>
@@ -14191,7 +14408,7 @@
         <v>0</v>
       </c>
       <c r="P77" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>46.4</v>
       </c>
       <c r="Q77" s="4">
@@ -14199,16 +14416,16 @@
         <v>403.19999999999993</v>
       </c>
       <c r="R77" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>403</v>
       </c>
       <c r="S77" s="21"/>
       <c r="T77" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.995689655172415</v>
       </c>
       <c r="U77" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.3103448275862073</v>
       </c>
       <c r="V77" s="5">
@@ -14243,10 +14460,13 @@
       </c>
       <c r="AF77" s="5"/>
       <c r="AG77" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>112.84000000000002</v>
       </c>
-      <c r="AH77" s="5"/>
+      <c r="AH77" s="5">
+        <f t="shared" si="25"/>
+        <v>12.992000000000001</v>
+      </c>
       <c r="AI77" s="5"/>
       <c r="AJ77" s="5"/>
       <c r="AK77" s="5"/>
@@ -14297,7 +14517,7 @@
         <v>210</v>
       </c>
       <c r="L78" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-16</v>
       </c>
       <c r="M78" s="5"/>
@@ -14306,7 +14526,7 @@
         <v>180</v>
       </c>
       <c r="P78" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>38.799999999999997</v>
       </c>
       <c r="Q78" s="4">
@@ -14314,16 +14534,16 @@
         <v>362.19999999999993</v>
       </c>
       <c r="R78" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>362</v>
       </c>
       <c r="S78" s="21"/>
       <c r="T78" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>13.994845360824744</v>
       </c>
       <c r="U78" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>4.6649484536082477</v>
       </c>
       <c r="V78" s="5">
@@ -14358,10 +14578,13 @@
       </c>
       <c r="AF78" s="5"/>
       <c r="AG78" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>101.36000000000001</v>
       </c>
-      <c r="AH78" s="5"/>
+      <c r="AH78" s="5">
+        <f t="shared" si="25"/>
+        <v>10.864000000000001</v>
+      </c>
       <c r="AI78" s="5"/>
       <c r="AJ78" s="5"/>
       <c r="AK78" s="5"/>
@@ -14412,7 +14635,7 @@
         <v>330</v>
       </c>
       <c r="L79" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M79" s="5"/>
@@ -14421,7 +14644,7 @@
         <v>0</v>
       </c>
       <c r="P79" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>65.400000000000006</v>
       </c>
       <c r="Q79" s="4">
@@ -14429,16 +14652,16 @@
         <v>561.40000000000009</v>
       </c>
       <c r="R79" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>561</v>
       </c>
       <c r="S79" s="21"/>
       <c r="T79" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>10.993883792048928</v>
       </c>
       <c r="U79" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.4159021406727827</v>
       </c>
       <c r="V79" s="5">
@@ -14473,10 +14696,13 @@
       </c>
       <c r="AF79" s="5"/>
       <c r="AG79" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>224.4</v>
       </c>
-      <c r="AH79" s="5"/>
+      <c r="AH79" s="5">
+        <f t="shared" si="25"/>
+        <v>26.160000000000004</v>
+      </c>
       <c r="AI79" s="5"/>
       <c r="AJ79" s="5"/>
       <c r="AK79" s="5"/>
@@ -14527,7 +14753,7 @@
         <v>14.2</v>
       </c>
       <c r="L80" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>2.5090000000000003</v>
       </c>
       <c r="M80" s="5"/>
@@ -14536,7 +14762,7 @@
         <v>0</v>
       </c>
       <c r="P80" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.3418000000000001</v>
       </c>
       <c r="Q80" s="4">
@@ -14544,56 +14770,59 @@
         <v>26.204799999999999</v>
       </c>
       <c r="R80" s="4">
+        <f t="shared" si="26"/>
+        <v>26</v>
+      </c>
+      <c r="S80" s="21"/>
+      <c r="T80" s="5">
+        <f t="shared" si="23"/>
+        <v>10.938715662217966</v>
+      </c>
+      <c r="U80" s="5">
+        <f t="shared" si="21"/>
+        <v>3.1584774672332272</v>
+      </c>
+      <c r="V80" s="5">
+        <v>5.8799999999999998E-2</v>
+      </c>
+      <c r="W80" s="5">
+        <v>1.8982000000000001</v>
+      </c>
+      <c r="X80" s="5">
+        <v>0.19040000000000001</v>
+      </c>
+      <c r="Y80" s="5">
+        <v>-0.51180000000000003</v>
+      </c>
+      <c r="Z80" s="5">
+        <v>6.7103999999999999</v>
+      </c>
+      <c r="AA80" s="5">
+        <v>5.0915999999999997</v>
+      </c>
+      <c r="AB80" s="5">
+        <v>3.8393999999999999</v>
+      </c>
+      <c r="AC80" s="5">
+        <v>4.0342000000000002</v>
+      </c>
+      <c r="AD80" s="5">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="AE80" s="5">
+        <v>3.0341999999999998</v>
+      </c>
+      <c r="AF80" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG80" s="5">
         <f t="shared" si="24"/>
         <v>26</v>
       </c>
-      <c r="S80" s="21"/>
-      <c r="T80" s="5">
-        <f t="shared" si="22"/>
-        <v>10.938715662217966</v>
-      </c>
-      <c r="U80" s="5">
-        <f t="shared" si="20"/>
-        <v>3.1584774672332272</v>
-      </c>
-      <c r="V80" s="5">
-        <v>5.8799999999999998E-2</v>
-      </c>
-      <c r="W80" s="5">
-        <v>1.8982000000000001</v>
-      </c>
-      <c r="X80" s="5">
-        <v>0.19040000000000001</v>
-      </c>
-      <c r="Y80" s="5">
-        <v>-0.51180000000000003</v>
-      </c>
-      <c r="Z80" s="5">
-        <v>6.7103999999999999</v>
-      </c>
-      <c r="AA80" s="5">
-        <v>5.0915999999999997</v>
-      </c>
-      <c r="AB80" s="5">
-        <v>3.8393999999999999</v>
-      </c>
-      <c r="AC80" s="5">
-        <v>4.0342000000000002</v>
-      </c>
-      <c r="AD80" s="5">
-        <v>9.1999999999999998E-2</v>
-      </c>
-      <c r="AE80" s="5">
-        <v>3.0341999999999998</v>
-      </c>
-      <c r="AF80" s="18" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG80" s="5">
-        <f t="shared" si="23"/>
-        <v>26</v>
-      </c>
-      <c r="AH80" s="5"/>
+      <c r="AH80" s="5">
+        <f t="shared" si="25"/>
+        <v>3.3418000000000001</v>
+      </c>
       <c r="AI80" s="5"/>
       <c r="AJ80" s="5"/>
       <c r="AK80" s="5"/>
@@ -14644,7 +14873,7 @@
         <v>11</v>
       </c>
       <c r="L81" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M81" s="5"/>
@@ -14653,21 +14882,21 @@
         <v>0</v>
       </c>
       <c r="P81" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.2000000000000002</v>
       </c>
       <c r="Q81" s="4"/>
       <c r="R81" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S81" s="21"/>
       <c r="T81" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>110.45454545454544</v>
       </c>
       <c r="U81" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>110.45454545454544</v>
       </c>
       <c r="V81" s="5">
@@ -14704,10 +14933,13 @@
         <v>104</v>
       </c>
       <c r="AG81" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH81" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH81" s="5">
+        <f t="shared" si="25"/>
+        <v>0.74360000000000015</v>
+      </c>
       <c r="AI81" s="5"/>
       <c r="AJ81" s="5"/>
       <c r="AK81" s="5"/>
@@ -14758,7 +14990,7 @@
         <v>21</v>
       </c>
       <c r="L82" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M82" s="5"/>
@@ -14767,21 +14999,21 @@
         <v>0</v>
       </c>
       <c r="P82" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>4.2</v>
       </c>
       <c r="Q82" s="4"/>
       <c r="R82" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S82" s="21"/>
       <c r="T82" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>78.80952380952381</v>
       </c>
       <c r="U82" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>78.80952380952381</v>
       </c>
       <c r="V82" s="5">
@@ -14818,10 +15050,13 @@
         <v>104</v>
       </c>
       <c r="AG82" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH82" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH82" s="5">
+        <f t="shared" si="25"/>
+        <v>1.3650000000000002</v>
+      </c>
       <c r="AI82" s="5"/>
       <c r="AJ82" s="5"/>
       <c r="AK82" s="5"/>
@@ -14872,7 +15107,7 @@
         <v>148</v>
       </c>
       <c r="L83" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>4</v>
       </c>
       <c r="M83" s="5"/>
@@ -14881,7 +15116,7 @@
         <v>0</v>
       </c>
       <c r="P83" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>30.4</v>
       </c>
       <c r="Q83" s="4">
@@ -14889,16 +15124,16 @@
         <v>285.79999999999995</v>
       </c>
       <c r="R83" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>286</v>
       </c>
       <c r="S83" s="21"/>
       <c r="T83" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.006578947368421</v>
       </c>
       <c r="U83" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>2.5986842105263159</v>
       </c>
       <c r="V83" s="5">
@@ -14933,10 +15168,13 @@
       </c>
       <c r="AF83" s="5"/>
       <c r="AG83" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>34.32</v>
       </c>
-      <c r="AH83" s="5"/>
+      <c r="AH83" s="5">
+        <f t="shared" si="25"/>
+        <v>3.6479999999999997</v>
+      </c>
       <c r="AI83" s="5"/>
       <c r="AJ83" s="5"/>
       <c r="AK83" s="5"/>
@@ -14987,7 +15225,7 @@
         <v>100</v>
       </c>
       <c r="L84" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-39</v>
       </c>
       <c r="M84" s="5"/>
@@ -14996,24 +15234,24 @@
         <v>150</v>
       </c>
       <c r="P84" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.2</v>
       </c>
       <c r="Q84" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>34</v>
       </c>
       <c r="R84" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>34</v>
       </c>
       <c r="S84" s="21"/>
       <c r="T84" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
       <c r="U84" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>12.213114754098362</v>
       </c>
       <c r="V84" s="5">
@@ -15048,10 +15286,13 @@
       </c>
       <c r="AF84" s="5"/>
       <c r="AG84" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>5.0999999999999996</v>
       </c>
-      <c r="AH84" s="5"/>
+      <c r="AH84" s="5">
+        <f t="shared" si="25"/>
+        <v>1.8299999999999998</v>
+      </c>
       <c r="AI84" s="5"/>
       <c r="AJ84" s="5"/>
       <c r="AK84" s="5"/>
@@ -15102,7 +15343,7 @@
         <v>84</v>
       </c>
       <c r="L85" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M85" s="5"/>
@@ -15111,21 +15352,21 @@
         <v>220</v>
       </c>
       <c r="P85" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.8</v>
       </c>
       <c r="Q85" s="4"/>
       <c r="R85" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S85" s="21"/>
       <c r="T85" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>20.952380952380953</v>
       </c>
       <c r="U85" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>20.952380952380953</v>
       </c>
       <c r="V85" s="5">
@@ -15162,10 +15403,13 @@
         <v>37</v>
       </c>
       <c r="AG85" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH85" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH85" s="5">
+        <f t="shared" si="25"/>
+        <v>2.52</v>
+      </c>
       <c r="AI85" s="5"/>
       <c r="AJ85" s="5"/>
       <c r="AK85" s="5"/>
@@ -15216,7 +15460,7 @@
         <v>64</v>
       </c>
       <c r="L86" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-6</v>
       </c>
       <c r="M86" s="5"/>
@@ -15225,21 +15469,21 @@
         <v>155</v>
       </c>
       <c r="P86" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.6</v>
       </c>
       <c r="Q86" s="4"/>
       <c r="R86" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S86" s="21"/>
       <c r="T86" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.379310344827587</v>
       </c>
       <c r="U86" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>16.379310344827587</v>
       </c>
       <c r="V86" s="5">
@@ -15274,10 +15518,13 @@
       </c>
       <c r="AF86" s="5"/>
       <c r="AG86" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH86" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH86" s="5">
+        <f t="shared" si="25"/>
+        <v>3.8279999999999998</v>
+      </c>
       <c r="AI86" s="5"/>
       <c r="AJ86" s="5"/>
       <c r="AK86" s="5"/>
@@ -15328,7 +15575,7 @@
         <v>383</v>
       </c>
       <c r="L87" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>5</v>
       </c>
       <c r="M87" s="5"/>
@@ -15337,7 +15584,7 @@
         <v>0</v>
       </c>
       <c r="P87" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>77.599999999999994</v>
       </c>
       <c r="Q87" s="4">
@@ -15345,16 +15592,16 @@
         <v>699.4</v>
       </c>
       <c r="R87" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>699</v>
       </c>
       <c r="S87" s="21"/>
       <c r="T87" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>8.9948453608247423</v>
       </c>
       <c r="U87" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>-1.2886597938144331E-2</v>
       </c>
       <c r="V87" s="5">
@@ -15391,10 +15638,13 @@
         <v>37</v>
       </c>
       <c r="AG87" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>104.85</v>
       </c>
-      <c r="AH87" s="5"/>
+      <c r="AH87" s="5">
+        <f t="shared" si="25"/>
+        <v>11.639999999999999</v>
+      </c>
       <c r="AI87" s="5"/>
       <c r="AJ87" s="5"/>
       <c r="AK87" s="5"/>
@@ -15445,7 +15695,7 @@
         <v>36</v>
       </c>
       <c r="L88" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-19</v>
       </c>
       <c r="M88" s="5"/>
@@ -15454,21 +15704,21 @@
         <v>50</v>
       </c>
       <c r="P88" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>3.4</v>
       </c>
       <c r="Q88" s="4"/>
       <c r="R88" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S88" s="21"/>
       <c r="T88" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>33.82352941176471</v>
       </c>
       <c r="U88" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>33.82352941176471</v>
       </c>
       <c r="V88" s="5">
@@ -15505,10 +15755,13 @@
         <v>139</v>
       </c>
       <c r="AG88" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH88" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH88" s="5">
+        <f t="shared" si="25"/>
+        <v>1.3939999999999999</v>
+      </c>
       <c r="AI88" s="5"/>
       <c r="AJ88" s="5"/>
       <c r="AK88" s="5"/>
@@ -15547,7 +15800,7 @@
       <c r="J89" s="9"/>
       <c r="K89" s="9"/>
       <c r="L89" s="9">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M89" s="9"/>
@@ -15556,12 +15809,12 @@
         <v>0</v>
       </c>
       <c r="P89" s="9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="Q89" s="11"/>
       <c r="R89" s="4">
-        <f t="shared" ref="R89" si="25">S89</f>
+        <f t="shared" ref="R89" si="27">S89</f>
         <v>100</v>
       </c>
       <c r="S89" s="21">
@@ -15569,11 +15822,11 @@
         <v>100</v>
       </c>
       <c r="T89" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U89" s="9" t="e">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V89" s="9">
@@ -15610,10 +15863,13 @@
         <v>141</v>
       </c>
       <c r="AG89" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>100</v>
       </c>
-      <c r="AH89" s="5"/>
+      <c r="AH89" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI89" s="5"/>
       <c r="AJ89" s="5"/>
       <c r="AK89" s="5"/>
@@ -15662,7 +15918,7 @@
         <v>117</v>
       </c>
       <c r="L90" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-37</v>
       </c>
       <c r="M90" s="5"/>
@@ -15671,7 +15927,7 @@
         <v>240</v>
       </c>
       <c r="P90" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16</v>
       </c>
       <c r="Q90" s="4">
@@ -15685,11 +15941,11 @@
         <v>200</v>
       </c>
       <c r="T90" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>22.5</v>
       </c>
       <c r="U90" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>15</v>
       </c>
       <c r="V90" s="5">
@@ -15724,10 +15980,13 @@
       </c>
       <c r="AF90" s="5"/>
       <c r="AG90" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>31.200000000000003</v>
       </c>
-      <c r="AH90" s="5"/>
+      <c r="AH90" s="5">
+        <f t="shared" si="25"/>
+        <v>4.16</v>
+      </c>
       <c r="AI90" s="5"/>
       <c r="AJ90" s="5"/>
       <c r="AK90" s="5"/>
@@ -15778,7 +16037,7 @@
         <v>51.7</v>
       </c>
       <c r="L91" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>7.4269999999999996</v>
       </c>
       <c r="M91" s="5"/>
@@ -15787,64 +16046,67 @@
         <v>60</v>
       </c>
       <c r="P91" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.8254</v>
       </c>
       <c r="Q91" s="4">
-        <f t="shared" ref="Q91:Q101" si="26">15*P91-O91-F91</f>
+        <f t="shared" ref="Q91:Q101" si="28">15*P91-O91-F91</f>
         <v>76.774000000000001</v>
       </c>
       <c r="R91" s="4">
+        <f t="shared" si="26"/>
+        <v>77</v>
+      </c>
+      <c r="S91" s="21"/>
+      <c r="T91" s="5">
+        <f t="shared" si="23"/>
+        <v>15.019111404265395</v>
+      </c>
+      <c r="U91" s="5">
+        <f t="shared" si="21"/>
+        <v>8.5077037563211384</v>
+      </c>
+      <c r="V91" s="5">
+        <v>9.8647999999999989</v>
+      </c>
+      <c r="W91" s="5">
+        <v>7.9896000000000003</v>
+      </c>
+      <c r="X91" s="5">
+        <v>10.4252</v>
+      </c>
+      <c r="Y91" s="5">
+        <v>9.0858000000000008</v>
+      </c>
+      <c r="Z91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE91" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF91" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG91" s="5">
         <f t="shared" si="24"/>
         <v>77</v>
       </c>
-      <c r="S91" s="21"/>
-      <c r="T91" s="5">
-        <f t="shared" si="22"/>
-        <v>15.019111404265395</v>
-      </c>
-      <c r="U91" s="5">
-        <f t="shared" si="20"/>
-        <v>8.5077037563211384</v>
-      </c>
-      <c r="V91" s="5">
-        <v>9.8647999999999989</v>
-      </c>
-      <c r="W91" s="5">
-        <v>7.9896000000000003</v>
-      </c>
-      <c r="X91" s="5">
-        <v>10.4252</v>
-      </c>
-      <c r="Y91" s="5">
-        <v>9.0858000000000008</v>
-      </c>
-      <c r="Z91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE91" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF91" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG91" s="5">
-        <f t="shared" si="23"/>
-        <v>77</v>
-      </c>
-      <c r="AH91" s="5"/>
+      <c r="AH91" s="5">
+        <f t="shared" si="25"/>
+        <v>11.8254</v>
+      </c>
       <c r="AI91" s="5"/>
       <c r="AJ91" s="5"/>
       <c r="AK91" s="5"/>
@@ -15895,7 +16157,7 @@
         <v>58</v>
       </c>
       <c r="L92" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-1</v>
       </c>
       <c r="M92" s="5"/>
@@ -15904,7 +16166,7 @@
         <v>201</v>
       </c>
       <c r="P92" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.4</v>
       </c>
       <c r="Q92" s="4"/>
@@ -15916,11 +16178,11 @@
         <v>100</v>
       </c>
       <c r="T92" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>27.456140350877192</v>
       </c>
       <c r="U92" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>24.82456140350877</v>
       </c>
       <c r="V92" s="5">
@@ -15955,10 +16217,13 @@
       </c>
       <c r="AF92" s="5"/>
       <c r="AG92" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>9.3000000000000007</v>
       </c>
-      <c r="AH92" s="5"/>
+      <c r="AH92" s="5">
+        <f t="shared" si="25"/>
+        <v>3.5340000000000003</v>
+      </c>
       <c r="AI92" s="5"/>
       <c r="AJ92" s="5"/>
       <c r="AK92" s="5"/>
@@ -16009,7 +16274,7 @@
         <v>34.4</v>
       </c>
       <c r="L93" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3.6579999999999977</v>
       </c>
       <c r="M93" s="5"/>
@@ -16018,64 +16283,67 @@
         <v>36</v>
       </c>
       <c r="P93" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>6.1484000000000005</v>
       </c>
       <c r="Q93" s="4">
+        <f t="shared" si="28"/>
+        <v>6.6350000000000122</v>
+      </c>
+      <c r="R93" s="4">
         <f t="shared" si="26"/>
-        <v>6.6350000000000122</v>
-      </c>
-      <c r="R93" s="4">
+        <v>7</v>
+      </c>
+      <c r="S93" s="21"/>
+      <c r="T93" s="5">
+        <f t="shared" si="23"/>
+        <v>15.059365038058681</v>
+      </c>
+      <c r="U93" s="5">
+        <f t="shared" si="21"/>
+        <v>13.920857458851083</v>
+      </c>
+      <c r="V93" s="5">
+        <v>9.2878000000000007</v>
+      </c>
+      <c r="W93" s="5">
+        <v>2.3904000000000001</v>
+      </c>
+      <c r="X93" s="5">
+        <v>8.8018000000000001</v>
+      </c>
+      <c r="Y93" s="5">
+        <v>6.4154</v>
+      </c>
+      <c r="Z93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF93" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG93" s="5">
         <f t="shared" si="24"/>
         <v>7</v>
       </c>
-      <c r="S93" s="21"/>
-      <c r="T93" s="5">
-        <f t="shared" si="22"/>
-        <v>15.059365038058681</v>
-      </c>
-      <c r="U93" s="5">
-        <f t="shared" si="20"/>
-        <v>13.920857458851083</v>
-      </c>
-      <c r="V93" s="5">
-        <v>9.2878000000000007</v>
-      </c>
-      <c r="W93" s="5">
-        <v>2.3904000000000001</v>
-      </c>
-      <c r="X93" s="5">
-        <v>8.8018000000000001</v>
-      </c>
-      <c r="Y93" s="5">
-        <v>6.4154</v>
-      </c>
-      <c r="Z93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AB93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AC93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AD93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AE93" s="5">
-        <v>0</v>
-      </c>
-      <c r="AF93" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG93" s="5">
-        <f t="shared" si="23"/>
-        <v>7</v>
-      </c>
-      <c r="AH93" s="5"/>
+      <c r="AH93" s="5">
+        <f t="shared" si="25"/>
+        <v>6.1484000000000005</v>
+      </c>
       <c r="AI93" s="5"/>
       <c r="AJ93" s="5"/>
       <c r="AK93" s="5"/>
@@ -16126,7 +16394,7 @@
         <v>60</v>
       </c>
       <c r="L94" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-3</v>
       </c>
       <c r="M94" s="5"/>
@@ -16135,24 +16403,24 @@
         <v>21</v>
       </c>
       <c r="P94" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>11.4</v>
       </c>
       <c r="Q94" s="4">
+        <f t="shared" si="28"/>
+        <v>64</v>
+      </c>
+      <c r="R94" s="4">
         <f t="shared" si="26"/>
         <v>64</v>
       </c>
-      <c r="R94" s="4">
-        <f t="shared" si="24"/>
-        <v>64</v>
-      </c>
       <c r="S94" s="21"/>
       <c r="T94" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15</v>
       </c>
       <c r="U94" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>9.3859649122807021</v>
       </c>
       <c r="V94" s="5">
@@ -16187,10 +16455,13 @@
       </c>
       <c r="AF94" s="5"/>
       <c r="AG94" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>25.6</v>
       </c>
-      <c r="AH94" s="5"/>
+      <c r="AH94" s="5">
+        <f t="shared" si="25"/>
+        <v>4.5600000000000005</v>
+      </c>
       <c r="AI94" s="5"/>
       <c r="AJ94" s="5"/>
       <c r="AK94" s="5"/>
@@ -16239,7 +16510,7 @@
         <v>106</v>
       </c>
       <c r="L95" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-25</v>
       </c>
       <c r="M95" s="5"/>
@@ -16248,7 +16519,7 @@
         <v>0</v>
       </c>
       <c r="P95" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>16.2</v>
       </c>
       <c r="Q95" s="4">
@@ -16264,11 +16535,11 @@
         <v>200</v>
       </c>
       <c r="T95" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>12.345679012345679</v>
       </c>
       <c r="U95" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="V95" s="5">
@@ -16305,10 +16576,13 @@
         <v>149</v>
       </c>
       <c r="AG95" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>70</v>
       </c>
-      <c r="AH95" s="5"/>
+      <c r="AH95" s="5">
+        <f t="shared" si="25"/>
+        <v>5.669999999999999</v>
+      </c>
       <c r="AI95" s="5"/>
       <c r="AJ95" s="5"/>
       <c r="AK95" s="5"/>
@@ -16359,7 +16633,7 @@
         <v>16.899999999999999</v>
       </c>
       <c r="L96" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-8.0579999999999981</v>
       </c>
       <c r="M96" s="5"/>
@@ -16368,21 +16642,21 @@
         <v>70</v>
       </c>
       <c r="P96" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>1.7684000000000002</v>
       </c>
       <c r="Q96" s="4"/>
       <c r="R96" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S96" s="21"/>
       <c r="T96" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>57.170323456231614</v>
       </c>
       <c r="U96" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>57.170323456231614</v>
       </c>
       <c r="V96" s="5">
@@ -16417,10 +16691,13 @@
       </c>
       <c r="AF96" s="5"/>
       <c r="AG96" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH96" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH96" s="5">
+        <f t="shared" si="25"/>
+        <v>1.7684000000000002</v>
+      </c>
       <c r="AI96" s="5"/>
       <c r="AJ96" s="5"/>
       <c r="AK96" s="5"/>
@@ -16471,7 +16748,7 @@
         <v>95.8</v>
       </c>
       <c r="L97" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-84.890999999999991</v>
       </c>
       <c r="M97" s="5"/>
@@ -16480,21 +16757,21 @@
         <v>0</v>
       </c>
       <c r="P97" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>2.1818</v>
       </c>
       <c r="Q97" s="4"/>
       <c r="R97" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S97" s="21"/>
       <c r="T97" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>57.754606288385737</v>
       </c>
       <c r="U97" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>57.754606288385737</v>
       </c>
       <c r="V97" s="5">
@@ -16529,10 +16806,13 @@
       </c>
       <c r="AF97" s="5"/>
       <c r="AG97" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH97" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH97" s="5">
+        <f t="shared" si="25"/>
+        <v>2.1818</v>
+      </c>
       <c r="AI97" s="5"/>
       <c r="AJ97" s="5"/>
       <c r="AK97" s="5"/>
@@ -16581,7 +16861,7 @@
         <v>211</v>
       </c>
       <c r="L98" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-149</v>
       </c>
       <c r="M98" s="5"/>
@@ -16590,15 +16870,15 @@
         <v>140</v>
       </c>
       <c r="P98" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.4</v>
       </c>
       <c r="Q98" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>46</v>
       </c>
       <c r="R98" s="4">
-        <f t="shared" ref="R98:R99" si="27">S98</f>
+        <f t="shared" ref="R98:R99" si="29">S98</f>
         <v>100</v>
       </c>
       <c r="S98" s="21">
@@ -16606,11 +16886,11 @@
         <v>100</v>
       </c>
       <c r="T98" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>19.35483870967742</v>
       </c>
       <c r="U98" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>11.29032258064516</v>
       </c>
       <c r="V98" s="5">
@@ -16647,10 +16927,13 @@
         <v>153</v>
       </c>
       <c r="AG98" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>33</v>
       </c>
-      <c r="AH98" s="5"/>
+      <c r="AH98" s="5">
+        <f t="shared" si="25"/>
+        <v>4.0920000000000005</v>
+      </c>
       <c r="AI98" s="5"/>
       <c r="AJ98" s="5"/>
       <c r="AK98" s="5"/>
@@ -16701,7 +16984,7 @@
         <v>143</v>
       </c>
       <c r="L99" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-80</v>
       </c>
       <c r="M99" s="5"/>
@@ -16710,15 +16993,15 @@
         <v>37</v>
       </c>
       <c r="P99" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>12.6</v>
       </c>
       <c r="Q99" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>77</v>
       </c>
       <c r="R99" s="4">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>100</v>
       </c>
       <c r="S99" s="21">
@@ -16726,11 +17009,11 @@
         <v>100</v>
       </c>
       <c r="T99" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.825396825396826</v>
       </c>
       <c r="U99" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>8.8888888888888893</v>
       </c>
       <c r="V99" s="5">
@@ -16767,10 +17050,13 @@
         <v>155</v>
       </c>
       <c r="AG99" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>10</v>
       </c>
-      <c r="AH99" s="5"/>
+      <c r="AH99" s="5">
+        <f t="shared" si="25"/>
+        <v>1.26</v>
+      </c>
       <c r="AI99" s="5"/>
       <c r="AJ99" s="5"/>
       <c r="AK99" s="5"/>
@@ -16821,7 +17107,7 @@
         <v>73</v>
       </c>
       <c r="L100" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M100" s="5"/>
@@ -16830,21 +17116,21 @@
         <v>200</v>
       </c>
       <c r="P100" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14.6</v>
       </c>
       <c r="Q100" s="4"/>
       <c r="R100" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S100" s="21"/>
       <c r="T100" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>21.712328767123289</v>
       </c>
       <c r="U100" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>21.712328767123289</v>
       </c>
       <c r="V100" s="5">
@@ -16881,10 +17167,13 @@
         <v>157</v>
       </c>
       <c r="AG100" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH100" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH100" s="5">
+        <f t="shared" si="25"/>
+        <v>1.46</v>
+      </c>
       <c r="AI100" s="5"/>
       <c r="AJ100" s="5"/>
       <c r="AK100" s="5"/>
@@ -16935,7 +17224,7 @@
         <v>222</v>
       </c>
       <c r="L101" s="5">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>-13</v>
       </c>
       <c r="M101" s="5"/>
@@ -16944,24 +17233,24 @@
         <v>180</v>
       </c>
       <c r="P101" s="5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>41.8</v>
       </c>
       <c r="Q101" s="4">
+        <f t="shared" si="28"/>
+        <v>375</v>
+      </c>
+      <c r="R101" s="4">
         <f t="shared" si="26"/>
         <v>375</v>
       </c>
-      <c r="R101" s="4">
-        <f t="shared" si="24"/>
-        <v>375</v>
-      </c>
       <c r="S101" s="21"/>
       <c r="T101" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>15.000000000000002</v>
       </c>
       <c r="U101" s="5">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>6.0287081339712927</v>
       </c>
       <c r="V101" s="5">
@@ -16996,10 +17285,13 @@
       </c>
       <c r="AF101" s="5"/>
       <c r="AG101" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>150</v>
       </c>
-      <c r="AH101" s="5"/>
+      <c r="AH101" s="5">
+        <f t="shared" si="25"/>
+        <v>16.72</v>
+      </c>
       <c r="AI101" s="5"/>
       <c r="AJ101" s="5"/>
       <c r="AK101" s="5"/>
@@ -17046,7 +17338,7 @@
         <v>8</v>
       </c>
       <c r="L102" s="13">
-        <f t="shared" ref="L102:L109" si="28">E102-K102</f>
+        <f t="shared" ref="L102:L109" si="30">E102-K102</f>
         <v>-13</v>
       </c>
       <c r="M102" s="13"/>
@@ -17055,21 +17347,21 @@
         <v>0</v>
       </c>
       <c r="P102" s="13">
-        <f t="shared" ref="P102:P109" si="29">E102/5</f>
+        <f t="shared" ref="P102:P109" si="31">E102/5</f>
         <v>-1</v>
       </c>
       <c r="Q102" s="15"/>
       <c r="R102" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S102" s="21"/>
       <c r="T102" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="U102" s="13">
-        <f t="shared" ref="U102:U109" si="30">(F102+O102)/P102</f>
+        <f t="shared" ref="U102:U109" si="32">(F102+O102)/P102</f>
         <v>0</v>
       </c>
       <c r="V102" s="13">
@@ -17106,10 +17398,13 @@
         <v>161</v>
       </c>
       <c r="AG102" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH102" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH102" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI102" s="5"/>
       <c r="AJ102" s="5"/>
       <c r="AK102" s="5"/>
@@ -17160,7 +17455,7 @@
         <v>13</v>
       </c>
       <c r="L103" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-14</v>
       </c>
       <c r="M103" s="13"/>
@@ -17169,21 +17464,21 @@
         <v>0</v>
       </c>
       <c r="P103" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>-0.2</v>
       </c>
       <c r="Q103" s="15"/>
       <c r="R103" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S103" s="21"/>
       <c r="T103" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>5</v>
       </c>
       <c r="U103" s="13">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="V103" s="13">
@@ -17220,10 +17515,13 @@
         <v>164</v>
       </c>
       <c r="AG103" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH103" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH103" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI103" s="5"/>
       <c r="AJ103" s="5"/>
       <c r="AK103" s="5"/>
@@ -17274,7 +17572,7 @@
         <v>4</v>
       </c>
       <c r="L104" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M104" s="5"/>
@@ -17283,21 +17581,21 @@
         <v>0</v>
       </c>
       <c r="P104" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0.8</v>
       </c>
       <c r="Q104" s="4"/>
       <c r="R104" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S104" s="21"/>
       <c r="T104" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>168.75</v>
       </c>
       <c r="U104" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>168.75</v>
       </c>
       <c r="V104" s="5">
@@ -17334,10 +17632,13 @@
         <v>104</v>
       </c>
       <c r="AG104" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH104" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH104" s="5">
+        <f t="shared" si="25"/>
+        <v>0.24</v>
+      </c>
       <c r="AI104" s="5"/>
       <c r="AJ104" s="5"/>
       <c r="AK104" s="5"/>
@@ -17387,7 +17688,7 @@
         <v>32</v>
       </c>
       <c r="L105" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-2</v>
       </c>
       <c r="M105" s="5"/>
@@ -17396,21 +17697,21 @@
         <v>165</v>
       </c>
       <c r="P105" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>6</v>
       </c>
       <c r="Q105" s="4"/>
       <c r="R105" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S105" s="21"/>
       <c r="T105" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>37</v>
       </c>
       <c r="U105" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>37</v>
       </c>
       <c r="V105" s="5">
@@ -17447,10 +17748,13 @@
         <v>166</v>
       </c>
       <c r="AG105" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH105" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH105" s="5">
+        <f t="shared" si="25"/>
+        <v>1.7999999999999998</v>
+      </c>
       <c r="AI105" s="5"/>
       <c r="AJ105" s="5"/>
       <c r="AK105" s="5"/>
@@ -17500,7 +17804,7 @@
         <v>14</v>
       </c>
       <c r="L106" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-5</v>
       </c>
       <c r="M106" s="5"/>
@@ -17509,7 +17813,7 @@
         <v>0</v>
       </c>
       <c r="P106" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>1.8</v>
       </c>
       <c r="Q106" s="4"/>
@@ -17521,11 +17825,11 @@
         <v>150</v>
       </c>
       <c r="T106" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>75.555555555555557</v>
       </c>
       <c r="U106" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>42.222222222222221</v>
       </c>
       <c r="V106" s="5">
@@ -17562,10 +17866,13 @@
         <v>170</v>
       </c>
       <c r="AG106" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
-      <c r="AH106" s="5"/>
+      <c r="AH106" s="5">
+        <f t="shared" si="25"/>
+        <v>0.18000000000000002</v>
+      </c>
       <c r="AI106" s="5"/>
       <c r="AJ106" s="5"/>
       <c r="AK106" s="5"/>
@@ -17616,7 +17923,7 @@
         <v>38</v>
       </c>
       <c r="L107" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>-1</v>
       </c>
       <c r="M107" s="5"/>
@@ -17625,7 +17932,7 @@
         <v>0</v>
       </c>
       <c r="P107" s="5">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>7.4</v>
       </c>
       <c r="Q107" s="4">
@@ -17640,11 +17947,11 @@
         <v>150</v>
       </c>
       <c r="T107" s="5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>16.351351351351351</v>
       </c>
       <c r="U107" s="5">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>0.13513513513513511</v>
       </c>
       <c r="V107" s="5">
@@ -17681,10 +17988,13 @@
         <v>167</v>
       </c>
       <c r="AG107" s="5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>12</v>
       </c>
-      <c r="AH107" s="5"/>
+      <c r="AH107" s="5">
+        <f t="shared" si="25"/>
+        <v>0.7400000000000001</v>
+      </c>
       <c r="AI107" s="5"/>
       <c r="AJ107" s="5"/>
       <c r="AK107" s="5"/>
@@ -17725,7 +18035,7 @@
       <c r="J108" s="13"/>
       <c r="K108" s="13"/>
       <c r="L108" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M108" s="13"/>
@@ -17734,21 +18044,21 @@
         <v>0</v>
       </c>
       <c r="P108" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Q108" s="15"/>
       <c r="R108" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S108" s="21"/>
       <c r="T108" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U108" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V108" s="13">
@@ -17785,10 +18095,13 @@
         <v>119</v>
       </c>
       <c r="AG108" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH108" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH108" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI108" s="5"/>
       <c r="AJ108" s="5"/>
       <c r="AK108" s="5"/>
@@ -17829,7 +18142,7 @@
       <c r="J109" s="13"/>
       <c r="K109" s="13"/>
       <c r="L109" s="13">
-        <f t="shared" si="28"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="M109" s="13"/>
@@ -17838,21 +18151,21 @@
         <v>0</v>
       </c>
       <c r="P109" s="13">
-        <f t="shared" si="29"/>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="Q109" s="15"/>
       <c r="R109" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="S109" s="21"/>
       <c r="T109" s="5" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>#DIV/0!</v>
       </c>
       <c r="U109" s="13" t="e">
-        <f t="shared" si="30"/>
+        <f t="shared" si="32"/>
         <v>#DIV/0!</v>
       </c>
       <c r="V109" s="13">
@@ -17889,10 +18202,13 @@
         <v>119</v>
       </c>
       <c r="AG109" s="5">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AH109" s="5"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="AH109" s="5">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
       <c r="AI109" s="5"/>
       <c r="AJ109" s="5"/>
       <c r="AK109" s="5"/>
